--- a/cypress/downloads/Employer_Summary.xlsx
+++ b/cypress/downloads/Employer_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <x:si>
     <x:t>Priority</x:t>
   </x:si>
@@ -88,7 +88,16 @@
     <x:t>Medium</x:t>
   </x:si>
   <x:si>
-    <x:t>nimal</x:t>
+    <x:t>recruiter emp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>out</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag 3 ,tag 2,tag 1,tag 3 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
   </x:si>
   <x:si>
     <x:t>Employer accreditation</x:t>
@@ -97,94 +106,70 @@
     <x:t>Approved</x:t>
   </x:si>
   <x:si>
-    <x:t>testing ny me nabeel</x:t>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>+64211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>http://pnytraininginsti.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Engineer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SQA update</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job Check</x:t>
+  </x:si>
+  <x:si>
+    <x:t>supplier emp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>outnz source</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0064211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>address 123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AgricultureFarming</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sqa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
   </x:si>
   <x:si>
     <x:t>1</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job Check</x:t>
-  </x:si>
-  <x:si>
-    <x:t>High</x:t>
-  </x:si>
-  <x:si>
-    <x:t>recruiter emp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>out</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tag 3 ,tag 2,tag 1,tag 3 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+64211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>http://pnytraininginsti.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Engineer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SQA update</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>lets see</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>supplier emp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>outnz source</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0064211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>address 123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AgricultureFarming</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2332</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sqa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
   </x:si>
   <x:si>
     <x:t>mlian</x:t>
@@ -251,8 +236,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:W9" totalsRowShown="0">
-  <x:autoFilter ref="A1:W9"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:W6" totalsRowShown="0">
+  <x:autoFilter ref="A1:W6"/>
   <x:tableColumns count="23">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="Name"/>
@@ -570,7 +555,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:W9"/>
+  <x:dimension ref="A1:W6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:23">
@@ -651,20 +636,41 @@
       <x:c r="B2" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="O2" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="P2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="R2" s="0" t="s">
+        <x:v>35</x:v>
       </x:c>
       <x:c r="U2" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="W2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:23">
@@ -674,108 +680,159 @@
       <x:c r="B3" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="J3" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>27</x:v>
+      <x:c r="N3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q3" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="R3" s="0" t="s">
+        <x:v>35</x:v>
       </x:c>
       <x:c r="U3" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="W3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:23">
       <x:c r="A4" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="P4" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q4" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R4" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="S4" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="T4" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
       <x:c r="U4" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="W4" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:23">
       <x:c r="A5" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="P5" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q5" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R5" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="S5" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="T5" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
       <x:c r="U5" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="W5" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:23">
@@ -783,151 +840,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="U6" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:23">
-      <x:c r="A7" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M7" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="P7" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="Q7" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="R7" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="S7" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="T7" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="U7" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="W7" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:23">
-      <x:c r="A8" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="P8" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="Q8" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="R8" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="S8" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="T8" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="U8" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="W8" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:23">
-      <x:c r="A9" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="U9" s="0" t="s">
-        <x:v>28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Employer_Summary.xlsx
+++ b/cypress/downloads/Employer_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <x:si>
     <x:t>Priority</x:t>
   </x:si>
@@ -88,88 +88,58 @@
     <x:t>Medium</x:t>
   </x:si>
   <x:si>
-    <x:t>recruiter emp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>out</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tag 3 ,tag 2,tag 1,tag 3 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Employer accreditation</x:t>
+    <x:t>supplier emp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>outnz source</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0064211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Employer Accreditation</x:t>
   </x:si>
   <x:si>
     <x:t>Approved</x:t>
   </x:si>
   <x:si>
+    <x:t>address 123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
     <x:t>test</x:t>
   </x:si>
   <x:si>
-    <x:t>+64211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>http://pnytraininginsti.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Engineer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SQA update</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
+    <x:t>AgricultureFarming</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sqa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
     <x:t>Job Check</x:t>
-  </x:si>
-  <x:si>
-    <x:t>supplier emp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>outnz source</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0064211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>address 123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AgricultureFarming</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2332</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sqa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
     <x:t>mlian</x:t>
@@ -236,8 +206,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:W6" totalsRowShown="0">
-  <x:autoFilter ref="A1:W6"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:W4" totalsRowShown="0">
+  <x:autoFilter ref="A1:W4"/>
   <x:tableColumns count="23">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="Name"/>
@@ -555,7 +525,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:W6"/>
+  <x:dimension ref="A1:W4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:23">
@@ -645,32 +615,47 @@
       <x:c r="G2" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O2" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P2" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="R2" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="S2" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N2" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="O2" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="P2" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="Q2" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="R2" s="0" t="s">
-        <x:v>35</x:v>
+      <x:c r="T2" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="U2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="W2" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:23">
@@ -689,32 +674,47 @@
       <x:c r="G3" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
       <x:c r="J3" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="Q3" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="R3" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="K3" s="0" t="s">
+      <x:c r="S3" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="P3" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="Q3" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="R3" s="0" t="s">
-        <x:v>35</x:v>
+      <x:c r="T3" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="U3" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="W3" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:23">
@@ -722,134 +722,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U4" s="0" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="R4" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="S4" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="T4" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="U4" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="W4" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:23">
-      <x:c r="A5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="P5" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="Q5" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="R5" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="S5" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="T5" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="U5" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="W5" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:23">
-      <x:c r="A6" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="U6" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Employer_Summary.xlsx
+++ b/cypress/downloads/Employer_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <x:si>
     <x:t>Priority</x:t>
   </x:si>
@@ -88,6 +88,24 @@
     <x:t>Medium</x:t>
   </x:si>
   <x:si>
+    <x:t>tsest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rwar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Employer Approval in Principal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cancelled</x:t>
+  </x:si>
+  <x:si>
     <x:t>supplier emp</x:t>
   </x:si>
   <x:si>
@@ -118,9 +136,6 @@
     <x:t>nabeel ahmed</x:t>
   </x:si>
   <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
     <x:t>AgricultureFarming</x:t>
   </x:si>
   <x:si>
@@ -143,6 +158,39 @@
   </x:si>
   <x:si>
     <x:t>mlian</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Client Awaiting Document Instructions</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Preparing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test new em</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 3 ,tag 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Couriered</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>High</x:t>
+  </x:si>
+  <x:si>
+    <x:t>employer</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag 3 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>milt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test@gmail.com</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -206,8 +254,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:W4" totalsRowShown="0">
-  <x:autoFilter ref="A1:W4"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:W12" totalsRowShown="0">
+  <x:autoFilter ref="A1:W12"/>
   <x:tableColumns count="23">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="Name"/>
@@ -525,7 +573,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:W4"/>
+  <x:dimension ref="A1:W12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:23">
@@ -609,53 +657,8 @@
       <x:c r="C2" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="U2" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="O2" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="P2" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="Q2" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="R2" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="S2" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="T2" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="U2" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="W2" s="0" t="s">
-        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:23">
@@ -663,58 +666,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="U3" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="P3" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="Q3" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="R3" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="T3" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="U3" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="W3" s="0" t="s">
-        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:23">
@@ -722,16 +683,251 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="P4" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="R4" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="J4" s="0" t="s">
+      <x:c r="S4" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="T4" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="U4" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="W4" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:23">
+      <x:c r="A5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="P5" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="U4" s="0" t="s">
-        <x:v>39</x:v>
+      <x:c r="R5" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="S5" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="T5" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="U5" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="W5" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:23">
+      <x:c r="A6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="U6" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:23">
+      <x:c r="A7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="U7" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:23">
+      <x:c r="A8" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="U8" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:23">
+      <x:c r="A9" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="U9" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="W9" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:23">
+      <x:c r="A10" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="U10" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="W10" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:23">
+      <x:c r="A11" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="U11" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:23">
+      <x:c r="A12" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="U12" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Employer_Summary.xlsx
+++ b/cypress/downloads/Employer_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <x:si>
     <x:t>Priority</x:t>
   </x:si>
@@ -97,70 +97,67 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
+    <x:t>supplier emp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>outnz source</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0064211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Employer accreditation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Approved</x:t>
+  </x:si>
+  <x:si>
+    <x:t>address 123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
     <x:t>test</x:t>
   </x:si>
   <x:si>
+    <x:t>AgricultureFarming</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sqa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job Check</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mlian</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Client Awaiting Document Instructions</x:t>
+  </x:si>
+  <x:si>
     <x:t>Employer Approval in Principal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cancelled</x:t>
-  </x:si>
-  <x:si>
-    <x:t>supplier emp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>outnz source</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0064211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Employer Accreditation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Approved</x:t>
-  </x:si>
-  <x:si>
-    <x:t>address 123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AgricultureFarming</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2332</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sqa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job Check</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mlian</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Client Awaiting Document Instructions</x:t>
   </x:si>
   <x:si>
     <x:t>Preparing</x:t>
@@ -254,8 +251,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:W12" totalsRowShown="0">
-  <x:autoFilter ref="A1:W12"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:W11" totalsRowShown="0">
+  <x:autoFilter ref="A1:W11"/>
   <x:tableColumns count="23">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="Name"/>
@@ -573,7 +570,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:W12"/>
+  <x:dimension ref="A1:W11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:23">
@@ -668,14 +665,56 @@
       <x:c r="B3" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="Q3" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="R3" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="T3" s="0" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="U3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="W3" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:23">
@@ -683,58 +722,58 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="H4" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="I4" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
+      <x:c r="J4" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="I4" s="0" t="s">
+      <x:c r="L4" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="J4" s="0" t="s">
+      <x:c r="M4" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
+      <x:c r="O4" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="L4" s="0" t="s">
+      <x:c r="P4" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="M4" s="0" t="s">
+      <x:c r="Q4" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="P4" s="0" t="s">
+      <x:c r="R4" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="Q4" s="0" t="s">
+      <x:c r="S4" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="T4" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="R4" s="0" t="s">
+      <x:c r="U4" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="S4" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="T4" s="0" t="s">
+      <x:c r="W4" s="0" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="U4" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="W4" s="0" t="s">
-        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:23">
@@ -742,58 +781,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
+      <x:c r="K5" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="P5" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="Q5" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="R5" s="0" t="s">
+      <x:c r="U5" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="S5" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="T5" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="U5" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="W5" s="0" t="s">
-        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:23">
@@ -801,16 +798,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="U6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:23">
@@ -818,16 +815,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="U7" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:23">
@@ -835,16 +832,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="U8" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="W8" s="0" t="s">
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:23">
@@ -852,81 +858,55 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="U9" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="W9" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="U9" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="W9" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:23">
       <x:c r="A10" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U10" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="W10" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:23">
       <x:c r="A11" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
       <x:c r="U11" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:23">
-      <x:c r="A12" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="U12" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/Employer_Summary.xlsx
+++ b/cypress/downloads/Employer_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <x:si>
     <x:t>Priority</x:t>
   </x:si>
@@ -118,37 +118,43 @@
     <x:t>Employer accreditation</x:t>
   </x:si>
   <x:si>
+    <x:t>Agreement Signed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>address 123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AgricultureFarming</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sqa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job Check</x:t>
+  </x:si>
+  <x:si>
     <x:t>Approved</x:t>
   </x:si>
   <x:si>
-    <x:t>address 123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AgricultureFarming</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2332</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sqa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job Check</x:t>
+    <x:t>Preparing</x:t>
   </x:si>
   <x:si>
     <x:t>mlian</x:t>
@@ -158,9 +164,6 @@
   </x:si>
   <x:si>
     <x:t>Employer Approval in Principal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Preparing</x:t>
   </x:si>
   <x:si>
     <x:t>test new em</x:t>
@@ -251,8 +254,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:W11" totalsRowShown="0">
-  <x:autoFilter ref="A1:W11"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:W13" totalsRowShown="0">
+  <x:autoFilter ref="A1:W13"/>
   <x:tableColumns count="23">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="Name"/>
@@ -570,7 +573,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:W11"/>
+  <x:dimension ref="A1:W13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:23">
@@ -781,16 +784,58 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>46</x:v>
+      <x:c r="L5" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P5" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="R5" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="S5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="T5" s="0" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="U5" s="0" t="s">
         <x:v>42</x:v>
+      </x:c>
+      <x:c r="W5" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:23">
@@ -798,16 +843,58 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P6" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="R6" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="S6" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="T6" s="0" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="U6" s="0" t="s">
         <x:v>42</x:v>
+      </x:c>
+      <x:c r="W6" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:23">
@@ -815,13 +902,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U7" s="0" t="s">
         <x:v>42</x:v>
@@ -832,25 +919,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U8" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="W8" s="0" t="s">
-        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:23">
@@ -858,39 +936,42 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U9" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="W9" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
     </x:row>
     <x:row r="10" spans="1:23">
       <x:c r="A10" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="U10" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="W10" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="U10" s="0" t="s">
-        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:23">
@@ -898,15 +979,55 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="U11" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="W11" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:23">
+      <x:c r="A12" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C11" s="0" t="s">
+      <x:c r="U12" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:23">
+      <x:c r="A13" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="U11" s="0" t="s">
+      <x:c r="G13" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="U13" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/Employer_Summary.xlsx
+++ b/cypress/downloads/Employer_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <x:si>
     <x:t>Priority</x:t>
   </x:si>
@@ -88,6 +88,60 @@
     <x:t>Medium</x:t>
   </x:si>
   <x:si>
+    <x:t>cy new employer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test sqa update</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03420811293</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test city</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Employer accreditation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Client Awaiting Document Instructions</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test address</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test website</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Administrative</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
     <x:t>tsest</x:t>
   </x:si>
   <x:si>
@@ -97,73 +151,22 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>supplier emp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>outnz source</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0064211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Employer accreditation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Agreement Signed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>address 123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AgricultureFarming</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2332</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sqa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel</x:t>
+    <x:t xml:space="preserve">default </x:t>
+  </x:si>
+  <x:si>
+    <x:t>mlian</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Employer Approval in Principal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Preparing</x:t>
   </x:si>
   <x:si>
     <x:t>Job Check</x:t>
   </x:si>
   <x:si>
     <x:t>Approved</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Preparing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mlian</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Client Awaiting Document Instructions</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Employer Approval in Principal</x:t>
   </x:si>
   <x:si>
     <x:t>test new em</x:t>
@@ -254,8 +257,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:W13" totalsRowShown="0">
-  <x:autoFilter ref="A1:W13"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:W11" totalsRowShown="0">
+  <x:autoFilter ref="A1:W11"/>
   <x:tableColumns count="23">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="Name"/>
@@ -573,7 +576,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:W13"/>
+  <x:dimension ref="A1:W11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:23">
@@ -657,8 +660,53 @@
       <x:c r="C2" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O2" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P2" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="R2" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="S2" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="T2" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
       <x:c r="U2" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="W2" s="0" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:23">
@@ -666,58 +714,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="P3" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="Q3" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="R3" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="T3" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="U3" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="W3" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:23">
@@ -725,58 +728,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="U4" s="0" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="R4" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="S4" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="T4" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="U4" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="W4" s="0" t="s">
-        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:23">
@@ -784,58 +739,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
+      <x:c r="K5" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="P5" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="Q5" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="R5" s="0" t="s">
+      <x:c r="U5" s="0" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="S5" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="T5" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="U5" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="W5" s="0" t="s">
-        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:23">
@@ -843,58 +756,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="M6" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="P6" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="Q6" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="R6" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="U6" s="0" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="S6" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="T6" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="U6" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="W6" s="0" t="s">
-        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:23">
@@ -902,16 +773,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U7" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:23">
@@ -919,16 +790,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="U8" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="W8" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:23">
@@ -936,42 +816,39 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="U9" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="W9" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:23">
       <x:c r="A10" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="U10" s="0" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="U10" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="W10" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:23">
@@ -979,56 +856,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="U11" s="0" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="U11" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="W11" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:23">
-      <x:c r="A12" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="U12" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:23">
-      <x:c r="A13" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="U13" s="0" t="s">
-        <x:v>26</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Employer_Summary.xlsx
+++ b/cypress/downloads/Employer_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <x:si>
     <x:t>Priority</x:t>
   </x:si>
@@ -88,7 +88,7 @@
     <x:t>Medium</x:t>
   </x:si>
   <x:si>
-    <x:t>cy new employer</x:t>
+    <x:t>supplier emp</x:t>
   </x:si>
   <x:si>
     <x:t>test sqa update</x:t>
@@ -130,55 +130,58 @@
     <x:t>test9</x:t>
   </x:si>
   <x:si>
+    <x:t>testwwwwwwwwwwww</x:t>
+  </x:si>
+  <x:si>
+    <x:t>restttttttttttttt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tsest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rwar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">default </x:t>
+  </x:si>
+  <x:si>
+    <x:t>mlian</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Job Check</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Approved</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Employer Approval in Principal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Preparing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test new em</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 3 ,tag 2</x:t>
+  </x:si>
+  <x:si>
     <x:t>test</x:t>
   </x:si>
   <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tsest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rwar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">default </x:t>
-  </x:si>
-  <x:si>
-    <x:t>mlian</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Employer Approval in Principal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Preparing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Job Check</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Approved</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test new em</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 3 ,tag 2</x:t>
+    <x:t>arsalan team member</x:t>
   </x:si>
   <x:si>
     <x:t>Couriered</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member</x:t>
   </x:si>
   <x:si>
     <x:t>High</x:t>
@@ -742,10 +745,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U5" s="0" t="s">
         <x:v>40</x:v>
@@ -759,10 +762,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U6" s="0" t="s">
         <x:v>40</x:v>
@@ -796,13 +799,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="U8" s="0" t="s">
         <x:v>40</x:v>
@@ -822,13 +825,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U9" s="0" t="s">
         <x:v>40</x:v>
@@ -839,13 +842,13 @@
     </x:row>
     <x:row r="10" spans="1:23">
       <x:c r="A10" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U10" s="0" t="s">
         <x:v>44</x:v>
@@ -856,13 +859,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U11" s="0" t="s">
         <x:v>44</x:v>
